--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>4.47</v>
+        <v>2.07</v>
       </c>
       <c r="M94" t="n">
-        <v>3.96</v>
+        <v>3.11</v>
       </c>
       <c r="N94" t="n">
-        <v>1.86</v>
+        <v>4.76</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,22 +11690,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,22 +12642,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,22 +12880,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,22 +12999,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,22 +13118,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,22 +16569,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G140" t="n">

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI140"/>
+  <dimension ref="A1:AI141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -975,27 +975,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>46073.39583333334</v>
+        <v>46073.375</v>
       </c>
     </row>
     <row r="6">
@@ -1094,27 +1094,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>46073.41666666666</v>
+        <v>46073.39583333334</v>
       </c>
     </row>
     <row r="7">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46073.4375</v>
+        <v>46073.41666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46073.5</v>
+        <v>46073.4375</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46073.51041666666</v>
+        <v>46073.5</v>
       </c>
     </row>
     <row r="15">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46073.52083333334</v>
+        <v>46073.51041666666</v>
       </c>
     </row>
     <row r="18">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>7.07</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46073.53125</v>
+        <v>46073.52083333334</v>
       </c>
     </row>
     <row r="20">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>7.07</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46073.58333333334</v>
+        <v>46073.53125</v>
       </c>
     </row>
     <row r="21">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
-        <v>46073.60416666666</v>
+        <v>46073.58333333334</v>
       </c>
     </row>
     <row r="39">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
-        <v>46073.625</v>
+        <v>46073.60416666666</v>
       </c>
     </row>
     <row r="44">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6083,7 +6083,7 @@
         <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
-        <v>46073.64583333334</v>
+        <v>46073.625</v>
       </c>
     </row>
     <row r="48">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7282,12 +7282,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7392,7 +7392,7 @@
         <v>0</v>
       </c>
       <c r="AI58" s="3" t="n">
-        <v>46073.65625</v>
+        <v>46073.64583333334</v>
       </c>
     </row>
     <row r="59">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7749,7 +7749,7 @@
         <v>0</v>
       </c>
       <c r="AI61" s="3" t="n">
-        <v>46073.66666666666</v>
+        <v>46073.65625</v>
       </c>
     </row>
     <row r="62">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="AI79" s="3" t="n">
-        <v>46073.67708333334</v>
+        <v>46073.66666666666</v>
       </c>
     </row>
     <row r="80">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10129,7 +10129,7 @@
         <v>0</v>
       </c>
       <c r="AI81" s="3" t="n">
-        <v>46073.6875</v>
+        <v>46073.67708333334</v>
       </c>
     </row>
     <row r="82">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11447,12 +11447,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11557,7 +11557,7 @@
         <v>0</v>
       </c>
       <c r="AI93" s="3" t="n">
-        <v>46073.69791666666</v>
+        <v>46073.6875</v>
       </c>
     </row>
     <row r="94">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>4.47</v>
+        <v>2.07</v>
       </c>
       <c r="M100" t="n">
-        <v>3.96</v>
+        <v>3.11</v>
       </c>
       <c r="N100" t="n">
-        <v>1.86</v>
+        <v>4.76</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12994,27 +12994,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13104,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="AI106" s="3" t="n">
-        <v>46073.70833333334</v>
+        <v>46073.69791666666</v>
       </c>
     </row>
     <row r="107">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,22 +13237,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,22 +13356,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13470,12 +13470,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13580,7 +13580,7 @@
         <v>0</v>
       </c>
       <c r="AI110" s="3" t="n">
-        <v>46073.73958333334</v>
+        <v>46073.70833333334</v>
       </c>
     </row>
     <row r="111">
@@ -13589,27 +13589,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13699,7 +13699,7 @@
         <v>0</v>
       </c>
       <c r="AI111" s="3" t="n">
-        <v>46073.75</v>
+        <v>46073.73958333334</v>
       </c>
     </row>
     <row r="112">
@@ -13708,7 +13708,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13818,7 +13818,7 @@
         <v>0</v>
       </c>
       <c r="AI112" s="3" t="n">
-        <v>46073.85416666666</v>
+        <v>46073.75</v>
       </c>
     </row>
     <row r="113">
@@ -13827,27 +13827,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L113" t="n">
@@ -13937,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="AI113" s="3" t="n">
-        <v>46073.875</v>
+        <v>46073.85416666666</v>
       </c>
     </row>
     <row r="114">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15887,7 +15887,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,22 +16331,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -17045,111 +17045,230 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Radnik Surdulica</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Napredak</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI140" s="3" t="n">
+        <v>46073.875</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
           <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Rudar Prijedor</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Radnik Bijeljina</t>
-        </is>
-      </c>
-      <c r="G140" t="n">
-        <v>0</v>
-      </c>
-      <c r="H140" t="n">
-        <v>0</v>
-      </c>
-      <c r="I140" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" t="inlineStr">
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Velež</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Željezničar</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L140" t="n">
-        <v>0</v>
-      </c>
-      <c r="M140" t="n">
-        <v>0</v>
-      </c>
-      <c r="N140" t="n">
-        <v>0</v>
-      </c>
-      <c r="O140" t="n">
-        <v>0</v>
-      </c>
-      <c r="P140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
-      <c r="R140" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" t="n">
-        <v>0</v>
-      </c>
-      <c r="T140" t="n">
-        <v>0</v>
-      </c>
-      <c r="U140" t="n">
-        <v>0</v>
-      </c>
-      <c r="V140" t="n">
-        <v>0</v>
-      </c>
-      <c r="W140" t="n">
-        <v>0</v>
-      </c>
-      <c r="X140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI140" s="3" t="n">
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI141" s="3" t="n">
         <v>46073.875</v>
       </c>
     </row>

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,22 +11571,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,22 +12999,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,22 +15379,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15887,7 +15887,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L130" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,22 +16331,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L137" t="n">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G141" t="n">

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,22 +11690,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,22 +12404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,22 +12642,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,22 +13237,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,22 +13356,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,22 +15379,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15649,7 +15649,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L137" t="n">
@@ -16807,22 +16807,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G141" t="n">

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="M28" t="n">
-        <v>4.04</v>
+        <v>4.56</v>
       </c>
       <c r="N28" t="n">
-        <v>4.93</v>
+        <v>6.58</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>6.58</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,22 +11571,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,22 +11690,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,22 +12404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.07</v>
+        <v>2.22</v>
       </c>
       <c r="M101" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="N101" t="n">
-        <v>4.76</v>
+        <v>2.97</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,22 +12880,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,22 +12999,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15649,7 +15649,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L128" t="n">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,22 +16807,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,22 +17164,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB141" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>6.58</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="M74" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N74" t="n">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,22 +11571,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,22 +11690,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.44</v>
+        <v>2.07</v>
       </c>
       <c r="M98" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="N98" t="n">
-        <v>2.47</v>
+        <v>4.76</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,22 +12642,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>4.47</v>
+        <v>1.8</v>
       </c>
       <c r="M103" t="n">
-        <v>3.96</v>
+        <v>3.52</v>
       </c>
       <c r="N103" t="n">
-        <v>1.86</v>
+        <v>4.42</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.8</v>
+        <v>2.44</v>
       </c>
       <c r="M104" t="n">
-        <v>3.52</v>
+        <v>3.38</v>
       </c>
       <c r="N104" t="n">
-        <v>4.42</v>
+        <v>2.47</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,22 +12999,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,22 +13237,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,22 +13356,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,22 +16926,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17077,7 +17077,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L140" t="n">
@@ -17164,22 +17164,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI141"/>
+  <dimension ref="A1:AI140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>6.58</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="M68" t="n">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="N68" t="n">
         <v>3.5</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,22 +11571,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,22 +12642,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,22 +12880,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>4.47</v>
+        <v>2.07</v>
       </c>
       <c r="M106" t="n">
-        <v>3.96</v>
+        <v>3.11</v>
       </c>
       <c r="N106" t="n">
-        <v>1.86</v>
+        <v>4.76</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,22 +16569,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,22 +16926,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17077,7 +17077,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L140" t="n">
@@ -17150,125 +17150,6 @@
         <v>0</v>
       </c>
       <c r="AI140" s="3" t="n">
-        <v>46073.875</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="n">
-        <v>46073</v>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Mačva Šabac</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Semendrija 1924</t>
-        </is>
-      </c>
-      <c r="G141" t="n">
-        <v>0</v>
-      </c>
-      <c r="H141" t="n">
-        <v>0</v>
-      </c>
-      <c r="I141" t="n">
-        <v>0</v>
-      </c>
-      <c r="J141" t="n">
-        <v>0</v>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L141" t="n">
-        <v>0</v>
-      </c>
-      <c r="M141" t="n">
-        <v>0</v>
-      </c>
-      <c r="N141" t="n">
-        <v>0</v>
-      </c>
-      <c r="O141" t="n">
-        <v>0</v>
-      </c>
-      <c r="P141" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
-      <c r="R141" t="n">
-        <v>0</v>
-      </c>
-      <c r="S141" t="n">
-        <v>0</v>
-      </c>
-      <c r="T141" t="n">
-        <v>0</v>
-      </c>
-      <c r="U141" t="n">
-        <v>0</v>
-      </c>
-      <c r="V141" t="n">
-        <v>0</v>
-      </c>
-      <c r="W141" t="n">
-        <v>0</v>
-      </c>
-      <c r="X141" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y141" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI141" s="3" t="n">
         <v>46073.875</v>
       </c>
     </row>

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.93</v>
+        <v>1.57</v>
       </c>
       <c r="M22" t="n">
-        <v>3.36</v>
+        <v>4.04</v>
       </c>
       <c r="N22" t="n">
-        <v>2.28</v>
+        <v>4.93</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>6.58</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L50" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7200,17 +7200,17 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="M73" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N73" t="n">
-        <v>3.5</v>
+        <v>3.77</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,22 +11571,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>4.47</v>
+        <v>3.45</v>
       </c>
       <c r="M99" t="n">
-        <v>3.96</v>
+        <v>3.3</v>
       </c>
       <c r="N99" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,22 +12404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.44</v>
+        <v>4.47</v>
       </c>
       <c r="M102" t="n">
-        <v>3.38</v>
+        <v>3.96</v>
       </c>
       <c r="N102" t="n">
-        <v>2.47</v>
+        <v>1.86</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,22 +12642,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,22 +12999,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,22 +13237,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,22 +13356,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L132" t="n">
@@ -16212,22 +16212,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,22 +16569,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17077,7 +17077,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L140" t="n">

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI140"/>
+  <dimension ref="A1:AI137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="M32" t="n">
-        <v>4.56</v>
+        <v>4.04</v>
       </c>
       <c r="N32" t="n">
-        <v>6.58</v>
+        <v>4.93</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,17 +6129,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.3</v>
+        <v>2.82</v>
       </c>
       <c r="M49" t="n">
-        <v>3.44</v>
+        <v>2.89</v>
       </c>
       <c r="N49" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.29</v>
+        <v>2.77</v>
       </c>
       <c r="M51" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="N51" t="n">
-        <v>3.05</v>
+        <v>2.38</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="M52" t="n">
-        <v>3.04</v>
+        <v>2.79</v>
       </c>
       <c r="N52" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.82</v>
+        <v>1.97</v>
       </c>
       <c r="M54" t="n">
-        <v>2.89</v>
+        <v>3.14</v>
       </c>
       <c r="N54" t="n">
-        <v>2.44</v>
+        <v>3.66</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.97</v>
+        <v>2.22</v>
       </c>
       <c r="M56" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="N56" t="n">
-        <v>3.66</v>
+        <v>3.12</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>4.73</v>
+        <v>2.3</v>
       </c>
       <c r="M57" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="N57" t="n">
-        <v>1.68</v>
+        <v>2.6</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
       <c r="M58" t="n">
-        <v>2.79</v>
+        <v>3.36</v>
       </c>
       <c r="N58" t="n">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="M66" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N66" t="n">
-        <v>3.5</v>
+        <v>3.77</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="M79" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N79" t="n">
-        <v>3.26</v>
+        <v>3.17</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.86</v>
+        <v>2.01</v>
       </c>
       <c r="M85" t="n">
-        <v>2.86</v>
+        <v>3.5</v>
       </c>
       <c r="N85" t="n">
-        <v>4.71</v>
+        <v>3.46</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>4.25</v>
+        <v>1.38</v>
       </c>
       <c r="M91" t="n">
-        <v>2.81</v>
+        <v>4.1</v>
       </c>
       <c r="N91" t="n">
-        <v>1.97</v>
+        <v>7.6</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.44</v>
+        <v>1.96</v>
       </c>
       <c r="M94" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="N94" t="n">
-        <v>2.47</v>
+        <v>3.37</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,22 +11690,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.22</v>
+        <v>4.47</v>
       </c>
       <c r="M95" t="n">
-        <v>3.2</v>
+        <v>3.96</v>
       </c>
       <c r="N95" t="n">
-        <v>2.97</v>
+        <v>1.86</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.96</v>
+        <v>2.26</v>
       </c>
       <c r="M96" t="n">
-        <v>3.42</v>
+        <v>3.61</v>
       </c>
       <c r="N96" t="n">
-        <v>3.37</v>
+        <v>3.05</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12404,22 +12404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>4.47</v>
+        <v>1.8</v>
       </c>
       <c r="M102" t="n">
-        <v>3.96</v>
+        <v>3.52</v>
       </c>
       <c r="N102" t="n">
-        <v>1.86</v>
+        <v>4.42</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,22 +13237,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.61</v>
+        <v>2.09</v>
       </c>
       <c r="M108" t="n">
-        <v>2.93</v>
+        <v>3.38</v>
       </c>
       <c r="N108" t="n">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13827,27 +13827,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13937,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="AI113" s="3" t="n">
-        <v>46073.85416666666</v>
+        <v>46073.75</v>
       </c>
     </row>
     <row r="114">
@@ -13946,27 +13946,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14056,7 +14056,7 @@
         <v>0</v>
       </c>
       <c r="AI114" s="3" t="n">
-        <v>46073.875</v>
+        <v>46073.75</v>
       </c>
     </row>
     <row r="115">
@@ -14065,12 +14065,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14175,7 +14175,7 @@
         <v>0</v>
       </c>
       <c r="AI115" s="3" t="n">
-        <v>46073.875</v>
+        <v>46073.75</v>
       </c>
     </row>
     <row r="116">
@@ -14184,12 +14184,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14294,7 +14294,7 @@
         <v>0</v>
       </c>
       <c r="AI116" s="3" t="n">
-        <v>46073.875</v>
+        <v>46073.75</v>
       </c>
     </row>
     <row r="117">
@@ -14303,27 +14303,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14413,7 +14413,7 @@
         <v>0</v>
       </c>
       <c r="AI117" s="3" t="n">
-        <v>46073.875</v>
+        <v>46073.85416666666</v>
       </c>
     </row>
     <row r="118">
@@ -14427,22 +14427,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15173,7 +15173,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L124" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L132" t="n">
@@ -16212,22 +16212,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16793,363 +16793,6 @@
         <v>0</v>
       </c>
       <c r="AI137" s="3" t="n">
-        <v>46073.875</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="n">
-        <v>46073</v>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Jedinstvo Ub</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Zemun</t>
-        </is>
-      </c>
-      <c r="G138" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" t="n">
-        <v>0</v>
-      </c>
-      <c r="I138" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L138" t="n">
-        <v>0</v>
-      </c>
-      <c r="M138" t="n">
-        <v>0</v>
-      </c>
-      <c r="N138" t="n">
-        <v>0</v>
-      </c>
-      <c r="O138" t="n">
-        <v>0</v>
-      </c>
-      <c r="P138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
-      <c r="R138" t="n">
-        <v>0</v>
-      </c>
-      <c r="S138" t="n">
-        <v>0</v>
-      </c>
-      <c r="T138" t="n">
-        <v>0</v>
-      </c>
-      <c r="U138" t="n">
-        <v>0</v>
-      </c>
-      <c r="V138" t="n">
-        <v>0</v>
-      </c>
-      <c r="W138" t="n">
-        <v>0</v>
-      </c>
-      <c r="X138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI138" s="3" t="n">
-        <v>46073.875</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="n">
-        <v>46073</v>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Tekstilac Odžaci</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Dinamo Jug</t>
-        </is>
-      </c>
-      <c r="G139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H139" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L139" t="n">
-        <v>0</v>
-      </c>
-      <c r="M139" t="n">
-        <v>0</v>
-      </c>
-      <c r="N139" t="n">
-        <v>0</v>
-      </c>
-      <c r="O139" t="n">
-        <v>0</v>
-      </c>
-      <c r="P139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0</v>
-      </c>
-      <c r="S139" t="n">
-        <v>0</v>
-      </c>
-      <c r="T139" t="n">
-        <v>0</v>
-      </c>
-      <c r="U139" t="n">
-        <v>0</v>
-      </c>
-      <c r="V139" t="n">
-        <v>0</v>
-      </c>
-      <c r="W139" t="n">
-        <v>0</v>
-      </c>
-      <c r="X139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI139" s="3" t="n">
-        <v>46073.875</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="n">
-        <v>46073</v>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Grafičar</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>FAP</t>
-        </is>
-      </c>
-      <c r="G140" t="n">
-        <v>0</v>
-      </c>
-      <c r="H140" t="n">
-        <v>0</v>
-      </c>
-      <c r="I140" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L140" t="n">
-        <v>0</v>
-      </c>
-      <c r="M140" t="n">
-        <v>0</v>
-      </c>
-      <c r="N140" t="n">
-        <v>0</v>
-      </c>
-      <c r="O140" t="n">
-        <v>0</v>
-      </c>
-      <c r="P140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
-      <c r="R140" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" t="n">
-        <v>0</v>
-      </c>
-      <c r="T140" t="n">
-        <v>0</v>
-      </c>
-      <c r="U140" t="n">
-        <v>0</v>
-      </c>
-      <c r="V140" t="n">
-        <v>0</v>
-      </c>
-      <c r="W140" t="n">
-        <v>0</v>
-      </c>
-      <c r="X140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI140" s="3" t="n">
         <v>46073.875</v>
       </c>
     </row>

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>6.58</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,17 +6129,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="M49" t="n">
-        <v>2.89</v>
+        <v>3.36</v>
       </c>
       <c r="N49" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>4.73</v>
+        <v>1.97</v>
       </c>
       <c r="M50" t="n">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="N50" t="n">
-        <v>1.68</v>
+        <v>3.66</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.77</v>
+        <v>2.29</v>
       </c>
       <c r="M51" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="N51" t="n">
-        <v>2.38</v>
+        <v>3.05</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="M52" t="n">
-        <v>2.79</v>
+        <v>2.89</v>
       </c>
       <c r="N52" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="M53" t="n">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="N53" t="n">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.22</v>
+        <v>4.73</v>
       </c>
       <c r="M56" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="N56" t="n">
-        <v>3.12</v>
+        <v>1.68</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.3</v>
+        <v>2.77</v>
       </c>
       <c r="M57" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="N57" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="M58" t="n">
-        <v>3.36</v>
+        <v>2.79</v>
       </c>
       <c r="N58" t="n">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="M62" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="M77" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N77" t="n">
-        <v>4.1</v>
+        <v>3.77</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>4.01</v>
+        <v>4.25</v>
       </c>
       <c r="M82" t="n">
-        <v>3.4</v>
+        <v>2.81</v>
       </c>
       <c r="N82" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.01</v>
+        <v>2.16</v>
       </c>
       <c r="M85" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N85" t="n">
-        <v>3.46</v>
+        <v>3.54</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>4.25</v>
+        <v>1.86</v>
       </c>
       <c r="M89" t="n">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="N89" t="n">
-        <v>1.97</v>
+        <v>4.71</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.38</v>
+        <v>2.01</v>
       </c>
       <c r="M91" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="N91" t="n">
-        <v>7.6</v>
+        <v>3.46</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="M94" t="n">
-        <v>3.42</v>
+        <v>3.52</v>
       </c>
       <c r="N94" t="n">
-        <v>3.37</v>
+        <v>4.42</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.26</v>
+        <v>4.47</v>
       </c>
       <c r="M96" t="n">
-        <v>3.61</v>
+        <v>3.96</v>
       </c>
       <c r="N96" t="n">
-        <v>3.05</v>
+        <v>1.86</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="M102" t="n">
-        <v>3.52</v>
+        <v>3.61</v>
       </c>
       <c r="N102" t="n">
-        <v>4.42</v>
+        <v>3.05</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.22</v>
+        <v>1.96</v>
       </c>
       <c r="M104" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="N104" t="n">
-        <v>2.97</v>
+        <v>3.37</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,22 +12999,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.44</v>
+        <v>2.07</v>
       </c>
       <c r="M106" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="N106" t="n">
-        <v>2.47</v>
+        <v>4.76</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,22 +13118,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.61</v>
+        <v>2.09</v>
       </c>
       <c r="M107" t="n">
-        <v>2.93</v>
+        <v>3.38</v>
       </c>
       <c r="N107" t="n">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,22 +13237,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.09</v>
+        <v>2.61</v>
       </c>
       <c r="M108" t="n">
-        <v>3.38</v>
+        <v>2.93</v>
       </c>
       <c r="N108" t="n">
-        <v>3.42</v>
+        <v>2.88</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,22 +13356,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,22 +13951,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14427,22 +14427,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14697,7 +14697,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15173,17 +15173,17 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G137" t="n">

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>6.58</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.3</v>
+        <v>4.73</v>
       </c>
       <c r="M48" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="N48" t="n">
-        <v>2.6</v>
+        <v>1.68</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="M49" t="n">
-        <v>3.36</v>
+        <v>3.04</v>
       </c>
       <c r="N49" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.97</v>
+        <v>2.22</v>
       </c>
       <c r="M50" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="N50" t="n">
-        <v>3.66</v>
+        <v>3.12</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6486,17 +6486,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="M52" t="n">
-        <v>2.89</v>
+        <v>3.36</v>
       </c>
       <c r="N52" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,17 +6962,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>4.73</v>
+        <v>1.97</v>
       </c>
       <c r="M56" t="n">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="N56" t="n">
-        <v>1.68</v>
+        <v>3.66</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.77</v>
+        <v>2.29</v>
       </c>
       <c r="M57" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="N57" t="n">
-        <v>2.38</v>
+        <v>3.05</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,10 +7323,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="M58" t="n">
-        <v>2.79</v>
+        <v>3.44</v>
       </c>
       <c r="N58" t="n">
         <v>2.6</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N62" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="M64" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.5</v>
+        <v>4.76</v>
       </c>
       <c r="M80" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N80" t="n">
-        <v>2.55</v>
+        <v>1.63</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>4.76</v>
+        <v>2.5</v>
       </c>
       <c r="M81" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N81" t="n">
-        <v>1.63</v>
+        <v>2.55</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>4.01</v>
+        <v>4.25</v>
       </c>
       <c r="M88" t="n">
-        <v>3.4</v>
+        <v>2.81</v>
       </c>
       <c r="N88" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.86</v>
+        <v>2.16</v>
       </c>
       <c r="M89" t="n">
-        <v>2.86</v>
+        <v>3.7</v>
       </c>
       <c r="N89" t="n">
-        <v>4.71</v>
+        <v>3.54</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,22 +11571,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="M94" t="n">
-        <v>3.52</v>
+        <v>3.61</v>
       </c>
       <c r="N94" t="n">
-        <v>4.42</v>
+        <v>3.05</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3.45</v>
+        <v>2.22</v>
       </c>
       <c r="M99" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N99" t="n">
-        <v>2</v>
+        <v>2.97</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.26</v>
+        <v>2.07</v>
       </c>
       <c r="M102" t="n">
-        <v>3.61</v>
+        <v>3.11</v>
       </c>
       <c r="N102" t="n">
-        <v>3.05</v>
+        <v>4.76</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.44</v>
+        <v>1.8</v>
       </c>
       <c r="M103" t="n">
-        <v>3.38</v>
+        <v>3.52</v>
       </c>
       <c r="N103" t="n">
-        <v>2.47</v>
+        <v>4.42</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.07</v>
+        <v>3.45</v>
       </c>
       <c r="M106" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="N106" t="n">
-        <v>4.76</v>
+        <v>2</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,22 +13118,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13356,22 +13356,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14697,7 +14697,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L120" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15292,7 +15292,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,22 +16093,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G137" t="n">

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>6.58</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>4.73</v>
+        <v>2.85</v>
       </c>
       <c r="M48" t="n">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="N48" t="n">
-        <v>1.68</v>
+        <v>2.22</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.77</v>
+        <v>2.3</v>
       </c>
       <c r="M49" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="N49" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.22</v>
+        <v>2.82</v>
       </c>
       <c r="M50" t="n">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="N50" t="n">
-        <v>3.12</v>
+        <v>2.44</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6605,17 +6605,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="M54" t="n">
-        <v>2.89</v>
+        <v>3.04</v>
       </c>
       <c r="N54" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="M57" t="n">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="N57" t="n">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="M58" t="n">
-        <v>3.44</v>
+        <v>2.99</v>
       </c>
       <c r="N58" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="M62" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="M69" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N69" t="n">
-        <v>4.1</v>
+        <v>3.77</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="M75" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N75" t="n">
-        <v>3.77</v>
+        <v>3.17</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.38</v>
+        <v>2.16</v>
       </c>
       <c r="M83" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="N83" t="n">
-        <v>7.6</v>
+        <v>3.54</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>4.25</v>
+        <v>1.38</v>
       </c>
       <c r="M88" t="n">
-        <v>2.81</v>
+        <v>4.1</v>
       </c>
       <c r="N88" t="n">
-        <v>1.97</v>
+        <v>7.6</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,22 +11571,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,22 +11690,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,55 +11726,55 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>4.47</v>
+        <v>2.44</v>
       </c>
       <c r="M95" t="n">
-        <v>3.96</v>
+        <v>3.38</v>
       </c>
       <c r="N95" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" t="n">
+        <v>0</v>
+      </c>
+      <c r="X95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB95" t="n">
         <v>1.86</v>
-      </c>
-      <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
-      <c r="R95" t="n">
-        <v>0</v>
-      </c>
-      <c r="S95" t="n">
-        <v>0</v>
-      </c>
-      <c r="T95" t="n">
-        <v>0</v>
-      </c>
-      <c r="U95" t="n">
-        <v>0</v>
-      </c>
-      <c r="V95" t="n">
-        <v>0</v>
-      </c>
-      <c r="W95" t="n">
-        <v>0</v>
-      </c>
-      <c r="X95" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y95" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB95" t="n">
-        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="M98" t="n">
-        <v>3.42</v>
+        <v>3.11</v>
       </c>
       <c r="N98" t="n">
-        <v>3.37</v>
+        <v>4.76</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.44</v>
+        <v>1.8</v>
       </c>
       <c r="M100" t="n">
-        <v>3.38</v>
+        <v>3.52</v>
       </c>
       <c r="N100" t="n">
-        <v>2.47</v>
+        <v>4.42</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,22 +12404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="M102" t="n">
-        <v>3.11</v>
+        <v>3.42</v>
       </c>
       <c r="N102" t="n">
-        <v>4.76</v>
+        <v>3.37</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,22 +12642,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>3.45</v>
+        <v>4.47</v>
       </c>
       <c r="M106" t="n">
-        <v>3.3</v>
+        <v>3.96</v>
       </c>
       <c r="N106" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15292,7 +15292,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,22 +16093,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,22 +16450,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G137" t="n">

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>6.58</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.93</v>
+        <v>6.14</v>
       </c>
       <c r="M36" t="n">
-        <v>3.36</v>
+        <v>4.1</v>
       </c>
       <c r="N36" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="M49" t="n">
-        <v>3.44</v>
+        <v>2.99</v>
       </c>
       <c r="N49" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.82</v>
+        <v>2.22</v>
       </c>
       <c r="M50" t="n">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="N50" t="n">
-        <v>2.44</v>
+        <v>3.12</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6724,17 +6724,17 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.77</v>
+        <v>2.3</v>
       </c>
       <c r="M54" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="N54" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="M55" t="n">
-        <v>2.79</v>
+        <v>3.04</v>
       </c>
       <c r="N55" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.97</v>
+        <v>2.72</v>
       </c>
       <c r="M56" t="n">
-        <v>3.14</v>
+        <v>2.79</v>
       </c>
       <c r="N56" t="n">
-        <v>3.66</v>
+        <v>2.6</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.22</v>
+        <v>1.97</v>
       </c>
       <c r="M57" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="N57" t="n">
-        <v>3.12</v>
+        <v>3.66</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.29</v>
+        <v>4.73</v>
       </c>
       <c r="M58" t="n">
-        <v>2.99</v>
+        <v>3.42</v>
       </c>
       <c r="N58" t="n">
-        <v>3.05</v>
+        <v>1.68</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N62" t="n">
-        <v>2.6</v>
+        <v>3.77</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,10 +8156,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="M65" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="N65" t="n">
         <v>3.5</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="M75" t="n">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="N75" t="n">
-        <v>3.17</v>
+        <v>3.5</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.85</v>
+        <v>2.27</v>
       </c>
       <c r="M76" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N76" t="n">
-        <v>4.1</v>
+        <v>3.26</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.27</v>
+        <v>1.85</v>
       </c>
       <c r="M77" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N77" t="n">
-        <v>3.26</v>
+        <v>4.1</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.86</v>
+        <v>2.01</v>
       </c>
       <c r="M82" t="n">
-        <v>2.86</v>
+        <v>3.5</v>
       </c>
       <c r="N82" t="n">
-        <v>4.71</v>
+        <v>3.46</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>4.01</v>
+        <v>1.38</v>
       </c>
       <c r="M86" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N86" t="n">
-        <v>1.88</v>
+        <v>7.6</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>4.25</v>
+        <v>4.01</v>
       </c>
       <c r="M87" t="n">
-        <v>2.81</v>
+        <v>3.4</v>
       </c>
       <c r="N87" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.38</v>
+        <v>1.86</v>
       </c>
       <c r="M88" t="n">
-        <v>4.1</v>
+        <v>2.86</v>
       </c>
       <c r="N88" t="n">
-        <v>7.6</v>
+        <v>4.71</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="M96" t="n">
-        <v>3.61</v>
+        <v>3.38</v>
       </c>
       <c r="N96" t="n">
-        <v>3.05</v>
+        <v>2.47</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.07</v>
+        <v>2.26</v>
       </c>
       <c r="M98" t="n">
-        <v>3.11</v>
+        <v>3.61</v>
       </c>
       <c r="N98" t="n">
-        <v>4.76</v>
+        <v>3.05</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>3.45</v>
+        <v>4.47</v>
       </c>
       <c r="M101" t="n">
-        <v>3.3</v>
+        <v>3.96</v>
       </c>
       <c r="N101" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.96</v>
+        <v>1.42</v>
       </c>
       <c r="M102" t="n">
-        <v>3.42</v>
+        <v>4.22</v>
       </c>
       <c r="N102" t="n">
-        <v>3.37</v>
+        <v>5.86</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,22 +12880,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.22</v>
+        <v>2.07</v>
       </c>
       <c r="M105" t="n">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="N105" t="n">
-        <v>2.97</v>
+        <v>4.76</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,22 +12999,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>4.47</v>
+        <v>1.8</v>
       </c>
       <c r="M106" t="n">
-        <v>3.96</v>
+        <v>3.52</v>
       </c>
       <c r="N106" t="n">
-        <v>1.86</v>
+        <v>4.42</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14578,7 +14578,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,22 +14784,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L123" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,22 +16450,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G137" t="n">

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>6.58</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>6.14</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>6.14</v>
+        <v>1.6</v>
       </c>
       <c r="M36" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="N36" t="n">
-        <v>1.5</v>
+        <v>4.83</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.55</v>
+        <v>2.55</v>
       </c>
       <c r="M45" t="n">
-        <v>4.4</v>
+        <v>2.95</v>
       </c>
       <c r="N45" t="n">
-        <v>4.86</v>
+        <v>2.85</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.55</v>
+        <v>1.55</v>
       </c>
       <c r="M46" t="n">
-        <v>2.95</v>
+        <v>4.4</v>
       </c>
       <c r="N46" t="n">
-        <v>2.85</v>
+        <v>4.86</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6248,17 +6248,17 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.22</v>
+        <v>4.73</v>
       </c>
       <c r="M50" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="N50" t="n">
-        <v>3.12</v>
+        <v>1.68</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="M51" t="n">
-        <v>2.89</v>
+        <v>3.04</v>
       </c>
       <c r="N51" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6724,17 +6724,17 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.3</v>
+        <v>2.82</v>
       </c>
       <c r="M54" t="n">
-        <v>3.44</v>
+        <v>2.89</v>
       </c>
       <c r="N54" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.77</v>
+        <v>2.3</v>
       </c>
       <c r="M55" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="N55" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.72</v>
+        <v>2.22</v>
       </c>
       <c r="M56" t="n">
-        <v>2.79</v>
+        <v>3.3</v>
       </c>
       <c r="N56" t="n">
-        <v>2.6</v>
+        <v>3.12</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.97</v>
+        <v>2.85</v>
       </c>
       <c r="M57" t="n">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N57" t="n">
-        <v>3.66</v>
+        <v>2.22</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>4.73</v>
+        <v>2.29</v>
       </c>
       <c r="M58" t="n">
-        <v>3.42</v>
+        <v>2.99</v>
       </c>
       <c r="N58" t="n">
-        <v>1.68</v>
+        <v>3.05</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="M62" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N62" t="n">
-        <v>3.77</v>
+        <v>3.17</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.01</v>
+        <v>4.25</v>
       </c>
       <c r="M82" t="n">
-        <v>3.5</v>
+        <v>2.81</v>
       </c>
       <c r="N82" t="n">
-        <v>3.46</v>
+        <v>1.97</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.38</v>
+        <v>2.16</v>
       </c>
       <c r="M86" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="N86" t="n">
-        <v>7.6</v>
+        <v>3.54</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.86</v>
+        <v>4.01</v>
       </c>
       <c r="M88" t="n">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="N88" t="n">
-        <v>4.71</v>
+        <v>1.88</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,22 +11690,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="M96" t="n">
-        <v>3.38</v>
+        <v>3.61</v>
       </c>
       <c r="N96" t="n">
-        <v>2.47</v>
+        <v>3.05</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.22</v>
+        <v>1.31</v>
       </c>
       <c r="M97" t="n">
-        <v>3.2</v>
+        <v>5.01</v>
       </c>
       <c r="N97" t="n">
-        <v>2.97</v>
+        <v>6.73</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.26</v>
+        <v>4.47</v>
       </c>
       <c r="M98" t="n">
-        <v>3.61</v>
+        <v>3.96</v>
       </c>
       <c r="N98" t="n">
-        <v>3.05</v>
+        <v>1.86</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3.45</v>
+        <v>1.96</v>
       </c>
       <c r="M99" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="N99" t="n">
-        <v>2</v>
+        <v>3.37</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,22 +12404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,55 +12440,55 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>4.47</v>
+        <v>2.44</v>
       </c>
       <c r="M101" t="n">
-        <v>3.96</v>
+        <v>3.38</v>
       </c>
       <c r="N101" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" t="n">
+        <v>0</v>
+      </c>
+      <c r="X101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB101" t="n">
         <v>1.86</v>
-      </c>
-      <c r="O101" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0</v>
-      </c>
-      <c r="S101" t="n">
-        <v>0</v>
-      </c>
-      <c r="T101" t="n">
-        <v>0</v>
-      </c>
-      <c r="U101" t="n">
-        <v>0</v>
-      </c>
-      <c r="V101" t="n">
-        <v>0</v>
-      </c>
-      <c r="W101" t="n">
-        <v>0</v>
-      </c>
-      <c r="X101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB101" t="n">
-        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>5.86</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,22 +12642,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.31</v>
+        <v>2</v>
       </c>
       <c r="M103" t="n">
-        <v>5.01</v>
+        <v>3.3</v>
       </c>
       <c r="N103" t="n">
-        <v>6.73</v>
+        <v>3.88</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.96</v>
+        <v>3.45</v>
       </c>
       <c r="M104" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="N104" t="n">
-        <v>3.37</v>
+        <v>2</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14578,7 +14578,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15173,7 +15173,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L124" t="n">

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>6.58</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6248,17 +6248,17 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>4.73</v>
+        <v>2.77</v>
       </c>
       <c r="M50" t="n">
-        <v>3.42</v>
+        <v>3.04</v>
       </c>
       <c r="N50" t="n">
-        <v>1.68</v>
+        <v>2.38</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="M51" t="n">
-        <v>3.04</v>
+        <v>2.79</v>
       </c>
       <c r="N51" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.72</v>
+        <v>1.97</v>
       </c>
       <c r="M52" t="n">
-        <v>2.79</v>
+        <v>3.14</v>
       </c>
       <c r="N52" t="n">
-        <v>2.6</v>
+        <v>3.66</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.97</v>
+        <v>2.29</v>
       </c>
       <c r="M53" t="n">
-        <v>3.14</v>
+        <v>2.99</v>
       </c>
       <c r="N53" t="n">
-        <v>3.66</v>
+        <v>3.05</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="M54" t="n">
-        <v>2.89</v>
+        <v>3.36</v>
       </c>
       <c r="N54" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.3</v>
+        <v>2.82</v>
       </c>
       <c r="M55" t="n">
-        <v>3.44</v>
+        <v>2.89</v>
       </c>
       <c r="N55" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="M56" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="N56" t="n">
-        <v>3.12</v>
+        <v>2.6</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.85</v>
+        <v>2.22</v>
       </c>
       <c r="M57" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="N57" t="n">
-        <v>2.22</v>
+        <v>3.12</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="M67" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N67" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="M68" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N68" t="n">
-        <v>2.6</v>
+        <v>3.77</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="M73" t="n">
-        <v>3.52</v>
+        <v>3.15</v>
       </c>
       <c r="N73" t="n">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="M76" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N76" t="n">
-        <v>3.26</v>
+        <v>3.17</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>4.01</v>
+        <v>1.86</v>
       </c>
       <c r="M88" t="n">
-        <v>3.4</v>
+        <v>2.86</v>
       </c>
       <c r="N88" t="n">
-        <v>1.88</v>
+        <v>4.71</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.01</v>
+        <v>1.38</v>
       </c>
       <c r="M89" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="N89" t="n">
-        <v>3.46</v>
+        <v>7.6</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,22 +11571,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="M94" t="n">
-        <v>3.5</v>
+        <v>4.22</v>
       </c>
       <c r="N94" t="n">
-        <v>3.39</v>
+        <v>5.86</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.42</v>
+        <v>3.45</v>
       </c>
       <c r="M95" t="n">
-        <v>4.22</v>
+        <v>3.3</v>
       </c>
       <c r="N95" t="n">
-        <v>5.86</v>
+        <v>2</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>3.45</v>
+        <v>2.1</v>
       </c>
       <c r="M104" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N104" t="n">
-        <v>2</v>
+        <v>3.39</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -13118,22 +13118,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.09</v>
+        <v>2.61</v>
       </c>
       <c r="M110" t="n">
-        <v>3.38</v>
+        <v>2.93</v>
       </c>
       <c r="N110" t="n">
-        <v>3.42</v>
+        <v>2.88</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,22 +14546,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,22 +14784,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15173,7 +15173,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L137" t="n">

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI137"/>
+  <dimension ref="A1:AI134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>6.14</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>6.58</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>6.14</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.55</v>
+        <v>1.55</v>
       </c>
       <c r="M45" t="n">
-        <v>2.95</v>
+        <v>4.4</v>
       </c>
       <c r="N45" t="n">
-        <v>2.85</v>
+        <v>4.86</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>4.73</v>
+        <v>2.29</v>
       </c>
       <c r="M49" t="n">
-        <v>3.42</v>
+        <v>2.99</v>
       </c>
       <c r="N49" t="n">
-        <v>1.68</v>
+        <v>3.05</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="M50" t="n">
-        <v>3.04</v>
+        <v>2.89</v>
       </c>
       <c r="N50" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,10 +6490,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="M51" t="n">
-        <v>2.79</v>
+        <v>3.44</v>
       </c>
       <c r="N51" t="n">
         <v>2.6</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6605,17 +6605,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.29</v>
+        <v>4.73</v>
       </c>
       <c r="M53" t="n">
-        <v>2.99</v>
+        <v>3.42</v>
       </c>
       <c r="N53" t="n">
-        <v>3.05</v>
+        <v>1.68</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="M54" t="n">
-        <v>3.36</v>
+        <v>2.79</v>
       </c>
       <c r="N54" t="n">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.82</v>
+        <v>1.97</v>
       </c>
       <c r="M55" t="n">
-        <v>2.89</v>
+        <v>3.14</v>
       </c>
       <c r="N55" t="n">
-        <v>2.44</v>
+        <v>3.66</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="M56" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="N56" t="n">
-        <v>2.6</v>
+        <v>3.12</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,14 +7204,14 @@
         </is>
       </c>
       <c r="L57" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="N57" t="n">
         <v>2.22</v>
       </c>
-      <c r="M57" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N57" t="n">
-        <v>3.12</v>
-      </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="M66" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N66" t="n">
-        <v>3.5</v>
+        <v>3.77</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="M67" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N67" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.83</v>
+        <v>2.27</v>
       </c>
       <c r="M68" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="N68" t="n">
-        <v>3.77</v>
+        <v>3.26</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.86</v>
+        <v>1.38</v>
       </c>
       <c r="M88" t="n">
-        <v>2.86</v>
+        <v>4.1</v>
       </c>
       <c r="N88" t="n">
-        <v>4.71</v>
+        <v>7.6</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.38</v>
+        <v>4.01</v>
       </c>
       <c r="M89" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N89" t="n">
-        <v>7.6</v>
+        <v>1.88</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>4.01</v>
+        <v>4.25</v>
       </c>
       <c r="M92" t="n">
-        <v>3.4</v>
+        <v>2.81</v>
       </c>
       <c r="N92" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,22 +11571,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="M94" t="n">
-        <v>4.22</v>
+        <v>3.3</v>
       </c>
       <c r="N94" t="n">
-        <v>5.86</v>
+        <v>3.88</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,22 +11690,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.45</v>
+        <v>2.1</v>
       </c>
       <c r="M95" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N95" t="n">
-        <v>2</v>
+        <v>3.39</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.26</v>
+        <v>2.07</v>
       </c>
       <c r="M96" t="n">
-        <v>3.61</v>
+        <v>3.11</v>
       </c>
       <c r="N96" t="n">
-        <v>3.05</v>
+        <v>4.76</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.31</v>
+        <v>1.8</v>
       </c>
       <c r="M97" t="n">
-        <v>5.01</v>
+        <v>3.52</v>
       </c>
       <c r="N97" t="n">
-        <v>6.73</v>
+        <v>4.42</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>4.47</v>
+        <v>1.96</v>
       </c>
       <c r="M98" t="n">
-        <v>3.96</v>
+        <v>3.42</v>
       </c>
       <c r="N98" t="n">
-        <v>1.86</v>
+        <v>3.37</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.96</v>
+        <v>2.26</v>
       </c>
       <c r="M99" t="n">
-        <v>3.42</v>
+        <v>3.61</v>
       </c>
       <c r="N99" t="n">
-        <v>3.37</v>
+        <v>3.05</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="M100" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="N100" t="n">
-        <v>2.97</v>
+        <v>2.47</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,22 +12404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.44</v>
+        <v>3.45</v>
       </c>
       <c r="M101" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="N101" t="n">
-        <v>2.47</v>
+        <v>2</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,22 +12642,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="M103" t="n">
-        <v>3.3</v>
+        <v>4.22</v>
       </c>
       <c r="N103" t="n">
-        <v>3.88</v>
+        <v>5.86</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,22 +12880,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.07</v>
+        <v>2.22</v>
       </c>
       <c r="M105" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="N105" t="n">
-        <v>4.76</v>
+        <v>2.97</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,22 +12999,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.8</v>
+        <v>4.47</v>
       </c>
       <c r="M106" t="n">
-        <v>3.52</v>
+        <v>3.96</v>
       </c>
       <c r="N106" t="n">
-        <v>4.42</v>
+        <v>1.86</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,22 +13356,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.61</v>
+        <v>2.09</v>
       </c>
       <c r="M110" t="n">
-        <v>2.93</v>
+        <v>3.38</v>
       </c>
       <c r="N110" t="n">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,22 +14546,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,22 +15379,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16436,363 +16436,6 @@
         <v>0</v>
       </c>
       <c r="AI134" s="3" t="n">
-        <v>46073.875</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="n">
-        <v>46073</v>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>OFK Vršac</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Borac Čačak</t>
-        </is>
-      </c>
-      <c r="G135" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" t="n">
-        <v>0</v>
-      </c>
-      <c r="I135" t="n">
-        <v>0</v>
-      </c>
-      <c r="J135" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L135" t="n">
-        <v>0</v>
-      </c>
-      <c r="M135" t="n">
-        <v>0</v>
-      </c>
-      <c r="N135" t="n">
-        <v>0</v>
-      </c>
-      <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
-      <c r="R135" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" t="n">
-        <v>0</v>
-      </c>
-      <c r="T135" t="n">
-        <v>0</v>
-      </c>
-      <c r="U135" t="n">
-        <v>0</v>
-      </c>
-      <c r="V135" t="n">
-        <v>0</v>
-      </c>
-      <c r="W135" t="n">
-        <v>0</v>
-      </c>
-      <c r="X135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI135" s="3" t="n">
-        <v>46073.875</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
-        <v>46073</v>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Jedinstvo Ub</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Zemun</t>
-        </is>
-      </c>
-      <c r="G136" t="n">
-        <v>0</v>
-      </c>
-      <c r="H136" t="n">
-        <v>0</v>
-      </c>
-      <c r="I136" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L136" t="n">
-        <v>0</v>
-      </c>
-      <c r="M136" t="n">
-        <v>0</v>
-      </c>
-      <c r="N136" t="n">
-        <v>0</v>
-      </c>
-      <c r="O136" t="n">
-        <v>0</v>
-      </c>
-      <c r="P136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
-      <c r="R136" t="n">
-        <v>0</v>
-      </c>
-      <c r="S136" t="n">
-        <v>0</v>
-      </c>
-      <c r="T136" t="n">
-        <v>0</v>
-      </c>
-      <c r="U136" t="n">
-        <v>0</v>
-      </c>
-      <c r="V136" t="n">
-        <v>0</v>
-      </c>
-      <c r="W136" t="n">
-        <v>0</v>
-      </c>
-      <c r="X136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI136" s="3" t="n">
-        <v>46073.875</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
-        <v>46073</v>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Slovenia PrvaLiga</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Mura</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Domžale</t>
-        </is>
-      </c>
-      <c r="G137" t="n">
-        <v>0</v>
-      </c>
-      <c r="H137" t="n">
-        <v>0</v>
-      </c>
-      <c r="I137" t="n">
-        <v>0</v>
-      </c>
-      <c r="J137" t="n">
-        <v>0</v>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>canceled</t>
-        </is>
-      </c>
-      <c r="L137" t="n">
-        <v>0</v>
-      </c>
-      <c r="M137" t="n">
-        <v>0</v>
-      </c>
-      <c r="N137" t="n">
-        <v>0</v>
-      </c>
-      <c r="O137" t="n">
-        <v>0</v>
-      </c>
-      <c r="P137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
-      <c r="R137" t="n">
-        <v>0</v>
-      </c>
-      <c r="S137" t="n">
-        <v>0</v>
-      </c>
-      <c r="T137" t="n">
-        <v>0</v>
-      </c>
-      <c r="U137" t="n">
-        <v>0</v>
-      </c>
-      <c r="V137" t="n">
-        <v>0</v>
-      </c>
-      <c r="W137" t="n">
-        <v>0</v>
-      </c>
-      <c r="X137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI137" s="3" t="n">
         <v>46073.875</v>
       </c>
     </row>

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6.14</v>
+        <v>1.6</v>
       </c>
       <c r="M21" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="N21" t="n">
-        <v>1.5</v>
+        <v>4.83</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>6.58</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>6.14</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.19</v>
+        <v>2.9</v>
       </c>
       <c r="M41" t="n">
-        <v>3.72</v>
+        <v>3.52</v>
       </c>
       <c r="N41" t="n">
-        <v>2.93</v>
+        <v>2.28</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.55</v>
+        <v>2.55</v>
       </c>
       <c r="M45" t="n">
-        <v>4.4</v>
+        <v>2.95</v>
       </c>
       <c r="N45" t="n">
-        <v>4.86</v>
+        <v>2.85</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6248,17 +6248,17 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="M50" t="n">
-        <v>2.89</v>
+        <v>3.36</v>
       </c>
       <c r="N50" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.3</v>
+        <v>4.73</v>
       </c>
       <c r="M51" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="N51" t="n">
-        <v>2.6</v>
+        <v>1.68</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6605,17 +6605,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>4.73</v>
+        <v>2.72</v>
       </c>
       <c r="M53" t="n">
-        <v>3.42</v>
+        <v>2.79</v>
       </c>
       <c r="N53" t="n">
-        <v>1.68</v>
+        <v>2.6</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.72</v>
+        <v>1.97</v>
       </c>
       <c r="M54" t="n">
-        <v>2.79</v>
+        <v>3.14</v>
       </c>
       <c r="N54" t="n">
-        <v>2.6</v>
+        <v>3.66</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.97</v>
+        <v>2.22</v>
       </c>
       <c r="M55" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="N55" t="n">
-        <v>3.66</v>
+        <v>3.12</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="M56" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="N56" t="n">
-        <v>3.12</v>
+        <v>2.6</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="M58" t="n">
-        <v>3.04</v>
+        <v>2.89</v>
       </c>
       <c r="N58" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="M68" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N68" t="n">
-        <v>3.26</v>
+        <v>3.17</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="M72" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N72" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="M77" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N77" t="n">
-        <v>3.5</v>
+        <v>3.77</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>4.76</v>
+        <v>2.5</v>
       </c>
       <c r="M80" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N80" t="n">
-        <v>1.63</v>
+        <v>2.55</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.5</v>
+        <v>4.76</v>
       </c>
       <c r="M81" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N81" t="n">
-        <v>2.55</v>
+        <v>1.63</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.38</v>
+        <v>4.25</v>
       </c>
       <c r="M88" t="n">
-        <v>4.1</v>
+        <v>2.81</v>
       </c>
       <c r="N88" t="n">
-        <v>7.6</v>
+        <v>1.97</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.86</v>
+        <v>2.16</v>
       </c>
       <c r="M91" t="n">
-        <v>2.86</v>
+        <v>3.7</v>
       </c>
       <c r="N91" t="n">
-        <v>4.71</v>
+        <v>3.54</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="M93" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N93" t="n">
-        <v>3.54</v>
+        <v>3.46</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="M94" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N94" t="n">
-        <v>3.88</v>
+        <v>2.97</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,22 +11690,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.1</v>
+        <v>4.47</v>
       </c>
       <c r="M95" t="n">
-        <v>3.5</v>
+        <v>3.96</v>
       </c>
       <c r="N95" t="n">
-        <v>3.39</v>
+        <v>1.86</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="M97" t="n">
-        <v>3.52</v>
+        <v>5.01</v>
       </c>
       <c r="N97" t="n">
-        <v>4.42</v>
+        <v>6.73</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="M98" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="N98" t="n">
-        <v>3.37</v>
+        <v>3.88</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.26</v>
+        <v>1.42</v>
       </c>
       <c r="M99" t="n">
-        <v>3.61</v>
+        <v>4.22</v>
       </c>
       <c r="N99" t="n">
-        <v>3.05</v>
+        <v>5.86</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.44</v>
+        <v>1.96</v>
       </c>
       <c r="M100" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="N100" t="n">
-        <v>2.47</v>
+        <v>3.37</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>3.45</v>
+        <v>2.26</v>
       </c>
       <c r="M101" t="n">
-        <v>3.3</v>
+        <v>3.61</v>
       </c>
       <c r="N101" t="n">
-        <v>2</v>
+        <v>3.05</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.31</v>
+        <v>2.1</v>
       </c>
       <c r="M102" t="n">
-        <v>5.01</v>
+        <v>3.5</v>
       </c>
       <c r="N102" t="n">
-        <v>6.73</v>
+        <v>3.39</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,22 +12642,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.42</v>
+        <v>2.44</v>
       </c>
       <c r="M103" t="n">
-        <v>4.22</v>
+        <v>3.38</v>
       </c>
       <c r="N103" t="n">
-        <v>5.86</v>
+        <v>2.47</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,22 +12880,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.22</v>
+        <v>3.45</v>
       </c>
       <c r="M105" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N105" t="n">
-        <v>2.97</v>
+        <v>2</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,22 +12999,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>4.47</v>
+        <v>1.8</v>
       </c>
       <c r="M106" t="n">
-        <v>3.96</v>
+        <v>3.52</v>
       </c>
       <c r="N106" t="n">
-        <v>1.86</v>
+        <v>4.42</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,22 +13118,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,22 +13237,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,22 +15379,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G134" t="n">

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6.58</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>6.14</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>6.14</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.93</v>
+        <v>1.4</v>
       </c>
       <c r="M29" t="n">
-        <v>3.36</v>
+        <v>4.56</v>
       </c>
       <c r="N29" t="n">
-        <v>2.28</v>
+        <v>6.58</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.29</v>
+        <v>1.97</v>
       </c>
       <c r="M48" t="n">
-        <v>2.99</v>
+        <v>3.14</v>
       </c>
       <c r="N48" t="n">
-        <v>3.05</v>
+        <v>3.66</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6248,17 +6248,17 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="M50" t="n">
-        <v>3.36</v>
+        <v>3.04</v>
       </c>
       <c r="N50" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>4.73</v>
+        <v>2.3</v>
       </c>
       <c r="M51" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="N51" t="n">
-        <v>1.68</v>
+        <v>2.6</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.77</v>
+        <v>2.22</v>
       </c>
       <c r="M52" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="N52" t="n">
-        <v>2.38</v>
+        <v>3.12</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.22</v>
+        <v>4.73</v>
       </c>
       <c r="M55" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="N55" t="n">
-        <v>3.12</v>
+        <v>1.68</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="M68" t="n">
         <v>3.2</v>
       </c>
       <c r="N68" t="n">
-        <v>3.17</v>
+        <v>3.5</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.38</v>
+        <v>2.16</v>
       </c>
       <c r="M83" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="N83" t="n">
-        <v>7.6</v>
+        <v>3.54</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>4.01</v>
+        <v>1.38</v>
       </c>
       <c r="M84" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N84" t="n">
-        <v>1.88</v>
+        <v>7.6</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>4.25</v>
+        <v>4.01</v>
       </c>
       <c r="M88" t="n">
-        <v>2.81</v>
+        <v>3.4</v>
       </c>
       <c r="N88" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="M91" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N91" t="n">
-        <v>3.54</v>
+        <v>3.46</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.01</v>
+        <v>4.25</v>
       </c>
       <c r="M93" t="n">
-        <v>3.5</v>
+        <v>2.81</v>
       </c>
       <c r="N93" t="n">
-        <v>3.46</v>
+        <v>1.97</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,22 +11571,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="M94" t="n">
-        <v>3.2</v>
+        <v>3.61</v>
       </c>
       <c r="N94" t="n">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,22 +11690,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>4.47</v>
+        <v>2.22</v>
       </c>
       <c r="M95" t="n">
-        <v>3.96</v>
+        <v>3.2</v>
       </c>
       <c r="N95" t="n">
-        <v>1.86</v>
+        <v>2.97</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.31</v>
+        <v>2.1</v>
       </c>
       <c r="M97" t="n">
-        <v>5.01</v>
+        <v>3.5</v>
       </c>
       <c r="N97" t="n">
-        <v>6.73</v>
+        <v>3.39</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.42</v>
+        <v>4.47</v>
       </c>
       <c r="M99" t="n">
-        <v>4.22</v>
+        <v>3.96</v>
       </c>
       <c r="N99" t="n">
-        <v>5.86</v>
+        <v>1.86</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="M100" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="N100" t="n">
-        <v>3.37</v>
+        <v>3.88</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,22 +12404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="M101" t="n">
-        <v>3.61</v>
+        <v>3.52</v>
       </c>
       <c r="N101" t="n">
-        <v>3.05</v>
+        <v>4.42</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="M102" t="n">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="N102" t="n">
-        <v>3.39</v>
+        <v>4.76</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,22 +12642,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.44</v>
+        <v>3.45</v>
       </c>
       <c r="M103" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="N103" t="n">
-        <v>2.47</v>
+        <v>2</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.07</v>
+        <v>2.44</v>
       </c>
       <c r="M104" t="n">
-        <v>3.11</v>
+        <v>3.38</v>
       </c>
       <c r="N104" t="n">
-        <v>4.76</v>
+        <v>2.47</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>3.45</v>
+        <v>1.42</v>
       </c>
       <c r="M105" t="n">
-        <v>3.3</v>
+        <v>4.22</v>
       </c>
       <c r="N105" t="n">
-        <v>2</v>
+        <v>5.86</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,22 +12999,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="M106" t="n">
-        <v>3.52</v>
+        <v>5.01</v>
       </c>
       <c r="N106" t="n">
-        <v>4.42</v>
+        <v>6.73</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13356,22 +13356,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.61</v>
+        <v>2.09</v>
       </c>
       <c r="M109" t="n">
-        <v>2.93</v>
+        <v>3.38</v>
       </c>
       <c r="N109" t="n">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.09</v>
+        <v>2.61</v>
       </c>
       <c r="M110" t="n">
-        <v>3.38</v>
+        <v>2.93</v>
       </c>
       <c r="N110" t="n">
-        <v>3.42</v>
+        <v>2.88</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14459,7 +14459,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,22 +14665,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L123" t="n">
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G134" t="n">

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="M22" t="n">
-        <v>4.04</v>
+        <v>4.56</v>
       </c>
       <c r="N22" t="n">
-        <v>4.93</v>
+        <v>6.58</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>6.14</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>6.58</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>6.14</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.85</v>
+        <v>2.29</v>
       </c>
       <c r="M49" t="n">
-        <v>3.36</v>
+        <v>2.99</v>
       </c>
       <c r="N49" t="n">
-        <v>2.22</v>
+        <v>3.05</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="M50" t="n">
-        <v>3.04</v>
+        <v>3.36</v>
       </c>
       <c r="N50" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.3</v>
+        <v>4.73</v>
       </c>
       <c r="M51" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="N51" t="n">
-        <v>2.6</v>
+        <v>1.68</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.22</v>
+        <v>2.82</v>
       </c>
       <c r="M52" t="n">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="N52" t="n">
-        <v>3.12</v>
+        <v>2.44</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="M53" t="n">
-        <v>2.79</v>
+        <v>3.04</v>
       </c>
       <c r="N53" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>4.73</v>
+        <v>2.3</v>
       </c>
       <c r="M55" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="N55" t="n">
-        <v>1.68</v>
+        <v>2.6</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.29</v>
+        <v>1.97</v>
       </c>
       <c r="M57" t="n">
-        <v>2.99</v>
+        <v>3.14</v>
       </c>
       <c r="N57" t="n">
-        <v>3.05</v>
+        <v>3.66</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.82</v>
+        <v>2.22</v>
       </c>
       <c r="M58" t="n">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="N58" t="n">
-        <v>2.44</v>
+        <v>3.12</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="N62" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="M64" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="N64" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.5</v>
+        <v>4.76</v>
       </c>
       <c r="M80" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N80" t="n">
-        <v>2.55</v>
+        <v>1.63</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>4.76</v>
+        <v>2.5</v>
       </c>
       <c r="M81" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N81" t="n">
-        <v>1.63</v>
+        <v>2.55</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.38</v>
+        <v>2.01</v>
       </c>
       <c r="M84" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="N84" t="n">
-        <v>7.6</v>
+        <v>3.46</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.86</v>
+        <v>2.16</v>
       </c>
       <c r="M90" t="n">
-        <v>2.86</v>
+        <v>3.7</v>
       </c>
       <c r="N90" t="n">
-        <v>4.71</v>
+        <v>3.54</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.01</v>
+        <v>4.01</v>
       </c>
       <c r="M91" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N91" t="n">
-        <v>3.46</v>
+        <v>1.88</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11571,22 +11571,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="M94" t="n">
-        <v>3.61</v>
+        <v>3.38</v>
       </c>
       <c r="N94" t="n">
-        <v>3.05</v>
+        <v>2.47</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,22 +11690,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="M95" t="n">
-        <v>3.2</v>
+        <v>3.61</v>
       </c>
       <c r="N95" t="n">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.96</v>
+        <v>2.22</v>
       </c>
       <c r="M96" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="N96" t="n">
-        <v>3.37</v>
+        <v>2.97</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="M97" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="N97" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>4.47</v>
+        <v>2.1</v>
       </c>
       <c r="M99" t="n">
-        <v>3.96</v>
+        <v>3.5</v>
       </c>
       <c r="N99" t="n">
-        <v>1.86</v>
+        <v>3.39</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="M100" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="N100" t="n">
-        <v>3.88</v>
+        <v>4.42</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="M101" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="N101" t="n">
-        <v>4.42</v>
+        <v>3.88</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>3.45</v>
+        <v>1.31</v>
       </c>
       <c r="M103" t="n">
-        <v>3.3</v>
+        <v>5.01</v>
       </c>
       <c r="N103" t="n">
-        <v>2</v>
+        <v>6.73</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.44</v>
+        <v>1.42</v>
       </c>
       <c r="M104" t="n">
-        <v>3.38</v>
+        <v>4.22</v>
       </c>
       <c r="N104" t="n">
-        <v>2.47</v>
+        <v>5.86</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.42</v>
+        <v>3.45</v>
       </c>
       <c r="M105" t="n">
-        <v>4.22</v>
+        <v>3.3</v>
       </c>
       <c r="N105" t="n">
-        <v>5.86</v>
+        <v>2</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.31</v>
+        <v>4.47</v>
       </c>
       <c r="M106" t="n">
-        <v>5.01</v>
+        <v>3.96</v>
       </c>
       <c r="N106" t="n">
-        <v>6.73</v>
+        <v>1.86</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,22 +13118,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,22 +13237,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,22 +13356,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.61</v>
+        <v>2.09</v>
       </c>
       <c r="M110" t="n">
-        <v>2.93</v>
+        <v>3.38</v>
       </c>
       <c r="N110" t="n">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14459,7 +14459,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,22 +14665,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16006,7 +16006,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,22 +16331,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.4</v>
+        <v>2.93</v>
       </c>
       <c r="M22" t="n">
-        <v>4.56</v>
+        <v>3.36</v>
       </c>
       <c r="N22" t="n">
-        <v>6.58</v>
+        <v>2.28</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.93</v>
+        <v>6.14</v>
       </c>
       <c r="M25" t="n">
-        <v>3.36</v>
+        <v>4.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>6.14</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.55</v>
+        <v>1.55</v>
       </c>
       <c r="M47" t="n">
-        <v>2.95</v>
+        <v>4.4</v>
       </c>
       <c r="N47" t="n">
-        <v>2.85</v>
+        <v>4.86</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.29</v>
+        <v>1.97</v>
       </c>
       <c r="M49" t="n">
-        <v>2.99</v>
+        <v>3.14</v>
       </c>
       <c r="N49" t="n">
-        <v>3.05</v>
+        <v>3.66</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6486,17 +6486,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="M52" t="n">
-        <v>2.89</v>
+        <v>3.04</v>
       </c>
       <c r="N52" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="M54" t="n">
-        <v>2.79</v>
+        <v>2.89</v>
       </c>
       <c r="N54" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.3</v>
+        <v>4.73</v>
       </c>
       <c r="M55" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="N55" t="n">
-        <v>2.6</v>
+        <v>1.68</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7081,17 +7081,17 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.97</v>
+        <v>2.29</v>
       </c>
       <c r="M57" t="n">
-        <v>3.14</v>
+        <v>2.99</v>
       </c>
       <c r="N57" t="n">
-        <v>3.66</v>
+        <v>3.05</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="M62" t="n">
-        <v>3.52</v>
+        <v>3.7</v>
       </c>
       <c r="N62" t="n">
-        <v>3.5</v>
+        <v>3.77</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="M64" t="n">
         <v>3.2</v>
       </c>
       <c r="N64" t="n">
-        <v>3.17</v>
+        <v>3.5</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="M69" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N69" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="M72" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N72" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.86</v>
+        <v>2.01</v>
       </c>
       <c r="M87" t="n">
-        <v>2.86</v>
+        <v>3.5</v>
       </c>
       <c r="N87" t="n">
-        <v>4.71</v>
+        <v>3.46</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>4.25</v>
+        <v>1.86</v>
       </c>
       <c r="M93" t="n">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="N93" t="n">
-        <v>1.97</v>
+        <v>4.71</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,22 +11690,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="M95" t="n">
-        <v>3.61</v>
+        <v>3.38</v>
       </c>
       <c r="N95" t="n">
-        <v>3.05</v>
+        <v>2.47</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.22</v>
+        <v>1.42</v>
       </c>
       <c r="M96" t="n">
-        <v>3.2</v>
+        <v>4.22</v>
       </c>
       <c r="N96" t="n">
-        <v>2.97</v>
+        <v>5.86</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.96</v>
+        <v>2.22</v>
       </c>
       <c r="M97" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="N97" t="n">
-        <v>3.37</v>
+        <v>2.97</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M99" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N99" t="n">
-        <v>3.39</v>
+        <v>3.88</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="M100" t="n">
-        <v>3.52</v>
+        <v>3.61</v>
       </c>
       <c r="N100" t="n">
-        <v>4.42</v>
+        <v>3.05</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="M101" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="N101" t="n">
-        <v>3.88</v>
+        <v>4.42</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.07</v>
+        <v>4.47</v>
       </c>
       <c r="M102" t="n">
-        <v>3.11</v>
+        <v>3.96</v>
       </c>
       <c r="N102" t="n">
-        <v>4.76</v>
+        <v>1.86</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="M104" t="n">
-        <v>4.22</v>
+        <v>3.5</v>
       </c>
       <c r="N104" t="n">
-        <v>5.86</v>
+        <v>3.39</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>4.47</v>
+        <v>2.07</v>
       </c>
       <c r="M106" t="n">
-        <v>3.96</v>
+        <v>3.11</v>
       </c>
       <c r="N106" t="n">
-        <v>1.86</v>
+        <v>4.76</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,22 +13356,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.09</v>
+        <v>2.61</v>
       </c>
       <c r="M110" t="n">
-        <v>3.38</v>
+        <v>2.93</v>
       </c>
       <c r="N110" t="n">
-        <v>3.42</v>
+        <v>2.88</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13951,22 +13951,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,22 +15617,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16006,7 +16006,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,22 +16331,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>6.14</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>6.14</v>
+        <v>2.93</v>
       </c>
       <c r="M25" t="n">
-        <v>4.1</v>
+        <v>3.36</v>
       </c>
       <c r="N25" t="n">
-        <v>1.5</v>
+        <v>2.28</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.55</v>
+        <v>1.55</v>
       </c>
       <c r="M45" t="n">
-        <v>2.95</v>
+        <v>4.4</v>
       </c>
       <c r="N45" t="n">
-        <v>2.85</v>
+        <v>4.86</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.55</v>
+        <v>2.55</v>
       </c>
       <c r="M47" t="n">
-        <v>4.4</v>
+        <v>2.95</v>
       </c>
       <c r="N47" t="n">
-        <v>4.86</v>
+        <v>2.85</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.97</v>
+        <v>2.82</v>
       </c>
       <c r="M49" t="n">
-        <v>3.14</v>
+        <v>2.89</v>
       </c>
       <c r="N49" t="n">
-        <v>3.66</v>
+        <v>2.44</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.85</v>
+        <v>4.73</v>
       </c>
       <c r="M50" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="N50" t="n">
-        <v>2.22</v>
+        <v>1.68</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6486,17 +6486,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.77</v>
+        <v>2.29</v>
       </c>
       <c r="M52" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="N52" t="n">
-        <v>2.38</v>
+        <v>3.05</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.82</v>
+        <v>1.97</v>
       </c>
       <c r="M54" t="n">
-        <v>2.89</v>
+        <v>3.14</v>
       </c>
       <c r="N54" t="n">
-        <v>2.44</v>
+        <v>3.66</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>4.73</v>
+        <v>2.85</v>
       </c>
       <c r="M55" t="n">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="N55" t="n">
-        <v>1.68</v>
+        <v>2.22</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="M56" t="n">
-        <v>2.79</v>
+        <v>3.44</v>
       </c>
       <c r="N56" t="n">
         <v>2.6</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.29</v>
+        <v>2.77</v>
       </c>
       <c r="M57" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="N57" t="n">
-        <v>3.05</v>
+        <v>2.38</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7319,17 +7319,17 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="M64" t="n">
-        <v>3.2</v>
+        <v>3.66</v>
       </c>
       <c r="N64" t="n">
-        <v>3.5</v>
+        <v>2.87</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.6</v>
+        <v>2.27</v>
       </c>
       <c r="M69" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N69" t="n">
-        <v>2.6</v>
+        <v>3.26</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>4.76</v>
+        <v>2.5</v>
       </c>
       <c r="M80" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N80" t="n">
-        <v>1.63</v>
+        <v>2.55</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.5</v>
+        <v>4.76</v>
       </c>
       <c r="M81" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N81" t="n">
-        <v>2.55</v>
+        <v>1.63</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.38</v>
+        <v>1.86</v>
       </c>
       <c r="M88" t="n">
-        <v>4.1</v>
+        <v>2.86</v>
       </c>
       <c r="N88" t="n">
-        <v>7.6</v>
+        <v>4.71</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>4.01</v>
+        <v>2.16</v>
       </c>
       <c r="M89" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N89" t="n">
-        <v>1.88</v>
+        <v>3.54</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,22 +11571,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="M95" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="N95" t="n">
-        <v>2.47</v>
+        <v>3.88</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.42</v>
+        <v>3.45</v>
       </c>
       <c r="M96" t="n">
-        <v>4.22</v>
+        <v>3.3</v>
       </c>
       <c r="N96" t="n">
-        <v>5.86</v>
+        <v>2</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="M97" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N97" t="n">
-        <v>2.97</v>
+        <v>3.39</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.96</v>
+        <v>2.26</v>
       </c>
       <c r="M98" t="n">
-        <v>3.42</v>
+        <v>3.61</v>
       </c>
       <c r="N98" t="n">
-        <v>3.37</v>
+        <v>3.05</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M99" t="n">
-        <v>3.3</v>
+        <v>3.11</v>
       </c>
       <c r="N99" t="n">
-        <v>3.88</v>
+        <v>4.76</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.26</v>
+        <v>1.96</v>
       </c>
       <c r="M100" t="n">
-        <v>3.61</v>
+        <v>3.42</v>
       </c>
       <c r="N100" t="n">
-        <v>3.05</v>
+        <v>3.37</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.8</v>
+        <v>2.22</v>
       </c>
       <c r="M101" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="N101" t="n">
-        <v>4.42</v>
+        <v>2.97</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>4.47</v>
+        <v>1.8</v>
       </c>
       <c r="M102" t="n">
-        <v>3.96</v>
+        <v>3.52</v>
       </c>
       <c r="N102" t="n">
-        <v>1.86</v>
+        <v>4.42</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,22 +12642,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.31</v>
+        <v>2.44</v>
       </c>
       <c r="M103" t="n">
-        <v>5.01</v>
+        <v>3.38</v>
       </c>
       <c r="N103" t="n">
-        <v>6.73</v>
+        <v>2.47</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>3.45</v>
+        <v>1.31</v>
       </c>
       <c r="M105" t="n">
-        <v>3.3</v>
+        <v>5.01</v>
       </c>
       <c r="N105" t="n">
-        <v>2</v>
+        <v>6.73</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.07</v>
+        <v>1.42</v>
       </c>
       <c r="M106" t="n">
-        <v>3.11</v>
+        <v>4.22</v>
       </c>
       <c r="N106" t="n">
-        <v>4.76</v>
+        <v>5.86</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,22 +13118,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,22 +13237,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,22 +13356,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.09</v>
+        <v>2.61</v>
       </c>
       <c r="M109" t="n">
-        <v>3.38</v>
+        <v>2.93</v>
       </c>
       <c r="N109" t="n">
-        <v>3.42</v>
+        <v>2.88</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.61</v>
+        <v>2.09</v>
       </c>
       <c r="M110" t="n">
-        <v>2.93</v>
+        <v>3.38</v>
       </c>
       <c r="N110" t="n">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,22 +13951,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14903,22 +14903,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,22 +15617,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15768,7 +15768,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L129" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G134" t="n">

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.4</v>
+        <v>2.93</v>
       </c>
       <c r="M28" t="n">
-        <v>4.56</v>
+        <v>3.36</v>
       </c>
       <c r="N28" t="n">
-        <v>6.58</v>
+        <v>2.28</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.19</v>
+        <v>2.9</v>
       </c>
       <c r="M42" t="n">
-        <v>3.72</v>
+        <v>3.52</v>
       </c>
       <c r="N42" t="n">
-        <v>2.93</v>
+        <v>2.28</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>4.73</v>
+        <v>1.97</v>
       </c>
       <c r="M50" t="n">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="N50" t="n">
-        <v>1.68</v>
+        <v>3.66</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="M51" t="n">
-        <v>2.79</v>
+        <v>2.89</v>
       </c>
       <c r="N51" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.29</v>
+        <v>2.72</v>
       </c>
       <c r="M52" t="n">
-        <v>2.99</v>
+        <v>2.79</v>
       </c>
       <c r="N52" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.22</v>
+        <v>4.73</v>
       </c>
       <c r="M53" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="N53" t="n">
-        <v>3.12</v>
+        <v>1.68</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="M56" t="n">
-        <v>3.44</v>
+        <v>2.99</v>
       </c>
       <c r="N56" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.77</v>
+        <v>2.22</v>
       </c>
       <c r="M57" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="N57" t="n">
-        <v>2.38</v>
+        <v>3.12</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7319,17 +7319,17 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="M70" t="n">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="N70" t="n">
-        <v>3.17</v>
+        <v>3.5</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.83</v>
+        <v>2.27</v>
       </c>
       <c r="M71" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="N71" t="n">
-        <v>3.77</v>
+        <v>3.26</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="M74" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N74" t="n">
-        <v>2.6</v>
+        <v>3.17</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="M76" t="n">
-        <v>3.52</v>
+        <v>3.66</v>
       </c>
       <c r="N76" t="n">
-        <v>3.5</v>
+        <v>2.87</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.5</v>
+        <v>4.76</v>
       </c>
       <c r="M80" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N80" t="n">
-        <v>2.55</v>
+        <v>1.63</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>4.76</v>
+        <v>2.5</v>
       </c>
       <c r="M81" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N81" t="n">
-        <v>1.63</v>
+        <v>2.55</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.86</v>
+        <v>4.01</v>
       </c>
       <c r="M88" t="n">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="N88" t="n">
-        <v>4.71</v>
+        <v>1.88</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.16</v>
+        <v>4.25</v>
       </c>
       <c r="M89" t="n">
-        <v>3.7</v>
+        <v>2.81</v>
       </c>
       <c r="N89" t="n">
-        <v>3.54</v>
+        <v>1.97</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,22 +11571,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>4.47</v>
+        <v>1.8</v>
       </c>
       <c r="M94" t="n">
-        <v>3.96</v>
+        <v>3.52</v>
       </c>
       <c r="N94" t="n">
-        <v>1.86</v>
+        <v>4.42</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,22 +11690,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2</v>
+        <v>1.31</v>
       </c>
       <c r="M95" t="n">
-        <v>3.3</v>
+        <v>5.01</v>
       </c>
       <c r="N95" t="n">
-        <v>3.88</v>
+        <v>6.73</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3.45</v>
+        <v>2.44</v>
       </c>
       <c r="M96" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="N96" t="n">
-        <v>2</v>
+        <v>2.47</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.1</v>
+        <v>4.47</v>
       </c>
       <c r="M97" t="n">
-        <v>3.5</v>
+        <v>3.96</v>
       </c>
       <c r="N97" t="n">
-        <v>3.39</v>
+        <v>1.86</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="M98" t="n">
-        <v>3.61</v>
+        <v>3.2</v>
       </c>
       <c r="N98" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M99" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="N99" t="n">
-        <v>4.76</v>
+        <v>3.88</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="M100" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="N100" t="n">
-        <v>3.37</v>
+        <v>3.39</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,22 +12404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="M101" t="n">
-        <v>3.2</v>
+        <v>3.61</v>
       </c>
       <c r="N101" t="n">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.8</v>
+        <v>3.45</v>
       </c>
       <c r="M102" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="N102" t="n">
-        <v>4.42</v>
+        <v>2</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,22 +12642,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.44</v>
+        <v>1.42</v>
       </c>
       <c r="M103" t="n">
-        <v>3.38</v>
+        <v>4.22</v>
       </c>
       <c r="N103" t="n">
-        <v>2.47</v>
+        <v>5.86</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,22 +12880,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.31</v>
+        <v>1.96</v>
       </c>
       <c r="M105" t="n">
-        <v>5.01</v>
+        <v>3.42</v>
       </c>
       <c r="N105" t="n">
-        <v>6.73</v>
+        <v>3.37</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,22 +12999,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>5.86</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13237,22 +13237,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,22 +13356,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,22 +14903,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15173,7 +15173,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L124" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15768,7 +15768,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,22 +16093,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G134" t="n">

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>6.14</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.57</v>
+        <v>2.93</v>
       </c>
       <c r="M29" t="n">
-        <v>4.04</v>
+        <v>3.36</v>
       </c>
       <c r="N29" t="n">
-        <v>4.93</v>
+        <v>2.28</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>6.58</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>6.14</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.09</v>
+        <v>1.4</v>
       </c>
       <c r="M36" t="n">
-        <v>3.32</v>
+        <v>4.56</v>
       </c>
       <c r="N36" t="n">
-        <v>3.41</v>
+        <v>6.58</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.55</v>
+        <v>1.55</v>
       </c>
       <c r="M47" t="n">
-        <v>2.95</v>
+        <v>4.4</v>
       </c>
       <c r="N47" t="n">
-        <v>2.85</v>
+        <v>4.86</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,17 +6129,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.97</v>
+        <v>4.73</v>
       </c>
       <c r="M50" t="n">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="N50" t="n">
-        <v>3.66</v>
+        <v>1.68</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.82</v>
+        <v>2.22</v>
       </c>
       <c r="M51" t="n">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="N51" t="n">
-        <v>2.44</v>
+        <v>3.12</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.72</v>
+        <v>2.29</v>
       </c>
       <c r="M52" t="n">
-        <v>2.79</v>
+        <v>2.99</v>
       </c>
       <c r="N52" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>4.73</v>
+        <v>2.85</v>
       </c>
       <c r="M53" t="n">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="N53" t="n">
-        <v>1.68</v>
+        <v>2.22</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.29</v>
+        <v>2.82</v>
       </c>
       <c r="M56" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="N56" t="n">
-        <v>3.05</v>
+        <v>2.44</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.22</v>
+        <v>2.72</v>
       </c>
       <c r="M57" t="n">
-        <v>3.3</v>
+        <v>2.79</v>
       </c>
       <c r="N57" t="n">
-        <v>3.12</v>
+        <v>2.6</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="M58" t="n">
-        <v>3.44</v>
+        <v>3.14</v>
       </c>
       <c r="N58" t="n">
-        <v>2.6</v>
+        <v>3.66</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="M70" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="N70" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="M71" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N71" t="n">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="M78" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N78" t="n">
-        <v>3.77</v>
+        <v>3.17</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>4.76</v>
+        <v>2.5</v>
       </c>
       <c r="M80" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N80" t="n">
-        <v>1.63</v>
+        <v>2.55</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.5</v>
+        <v>4.76</v>
       </c>
       <c r="M81" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N81" t="n">
-        <v>2.55</v>
+        <v>1.63</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.38</v>
+        <v>4.01</v>
       </c>
       <c r="M85" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N85" t="n">
-        <v>7.6</v>
+        <v>1.88</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>4.01</v>
+        <v>4.25</v>
       </c>
       <c r="M88" t="n">
-        <v>3.4</v>
+        <v>2.81</v>
       </c>
       <c r="N88" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="M90" t="n">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="N90" t="n">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.01</v>
+        <v>1.86</v>
       </c>
       <c r="M93" t="n">
-        <v>3.5</v>
+        <v>2.86</v>
       </c>
       <c r="N93" t="n">
-        <v>3.46</v>
+        <v>4.71</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,22 +11571,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.8</v>
+        <v>3.45</v>
       </c>
       <c r="M94" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="N94" t="n">
-        <v>4.42</v>
+        <v>2</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.44</v>
+        <v>4.47</v>
       </c>
       <c r="M96" t="n">
-        <v>3.38</v>
+        <v>3.96</v>
       </c>
       <c r="N96" t="n">
-        <v>2.47</v>
+        <v>1.86</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>4.47</v>
+        <v>2.1</v>
       </c>
       <c r="M97" t="n">
-        <v>3.96</v>
+        <v>3.5</v>
       </c>
       <c r="N97" t="n">
-        <v>1.86</v>
+        <v>3.39</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="M98" t="n">
-        <v>3.2</v>
+        <v>3.61</v>
       </c>
       <c r="N98" t="n">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="M99" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="N99" t="n">
-        <v>3.88</v>
+        <v>2.47</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M100" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N100" t="n">
-        <v>3.39</v>
+        <v>3.88</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.26</v>
+        <v>1.42</v>
       </c>
       <c r="M101" t="n">
-        <v>3.61</v>
+        <v>4.22</v>
       </c>
       <c r="N101" t="n">
-        <v>3.05</v>
+        <v>5.86</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>3.45</v>
+        <v>2.22</v>
       </c>
       <c r="M102" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N102" t="n">
-        <v>2</v>
+        <v>2.97</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,22 +12642,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.42</v>
+        <v>1.96</v>
       </c>
       <c r="M103" t="n">
-        <v>4.22</v>
+        <v>3.42</v>
       </c>
       <c r="N103" t="n">
-        <v>5.86</v>
+        <v>3.37</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,22 +12880,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="M105" t="n">
-        <v>3.42</v>
+        <v>3.11</v>
       </c>
       <c r="N105" t="n">
-        <v>3.37</v>
+        <v>4.76</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13237,22 +13237,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.61</v>
+        <v>2.09</v>
       </c>
       <c r="M108" t="n">
-        <v>2.93</v>
+        <v>3.38</v>
       </c>
       <c r="N108" t="n">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.09</v>
+        <v>2.61</v>
       </c>
       <c r="M110" t="n">
-        <v>3.38</v>
+        <v>2.93</v>
       </c>
       <c r="N110" t="n">
-        <v>3.42</v>
+        <v>2.88</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,22 +14546,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L122" t="n">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15173,7 +15173,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L124" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,22 +16093,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G134" t="n">

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>6.14</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>6.14</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>6.58</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.6</v>
+        <v>2.09</v>
       </c>
       <c r="M37" t="n">
-        <v>3.95</v>
+        <v>3.32</v>
       </c>
       <c r="N37" t="n">
-        <v>4.83</v>
+        <v>3.41</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.9</v>
+        <v>2.19</v>
       </c>
       <c r="M42" t="n">
-        <v>3.52</v>
+        <v>3.72</v>
       </c>
       <c r="N42" t="n">
-        <v>2.28</v>
+        <v>2.93</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.3</v>
+        <v>2.82</v>
       </c>
       <c r="M49" t="n">
-        <v>3.44</v>
+        <v>2.89</v>
       </c>
       <c r="N49" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>4.73</v>
+        <v>2.29</v>
       </c>
       <c r="M50" t="n">
-        <v>3.42</v>
+        <v>2.99</v>
       </c>
       <c r="N50" t="n">
-        <v>1.68</v>
+        <v>3.05</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="M51" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="N51" t="n">
-        <v>3.12</v>
+        <v>2.6</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.29</v>
+        <v>2.85</v>
       </c>
       <c r="M52" t="n">
-        <v>2.99</v>
+        <v>3.36</v>
       </c>
       <c r="N52" t="n">
-        <v>3.05</v>
+        <v>2.22</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.85</v>
+        <v>2.22</v>
       </c>
       <c r="M53" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="N53" t="n">
-        <v>2.22</v>
+        <v>3.12</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="M54" t="n">
-        <v>3.04</v>
+        <v>2.79</v>
       </c>
       <c r="N54" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.82</v>
+        <v>4.73</v>
       </c>
       <c r="M56" t="n">
-        <v>2.89</v>
+        <v>3.42</v>
       </c>
       <c r="N56" t="n">
-        <v>2.44</v>
+        <v>1.68</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="M57" t="n">
-        <v>2.79</v>
+        <v>3.04</v>
       </c>
       <c r="N57" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="M70" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N70" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="M71" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N71" t="n">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="M75" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N75" t="n">
-        <v>4.1</v>
+        <v>3.17</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.09</v>
+        <v>1.83</v>
       </c>
       <c r="M77" t="n">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="N77" t="n">
-        <v>2.87</v>
+        <v>3.77</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.5</v>
+        <v>4.76</v>
       </c>
       <c r="M80" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N80" t="n">
-        <v>2.55</v>
+        <v>1.63</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>4.76</v>
+        <v>2.5</v>
       </c>
       <c r="M81" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N81" t="n">
-        <v>1.63</v>
+        <v>2.55</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.01</v>
+        <v>4.01</v>
       </c>
       <c r="M82" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N82" t="n">
-        <v>3.46</v>
+        <v>1.88</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>4.01</v>
+        <v>2.16</v>
       </c>
       <c r="M85" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N85" t="n">
-        <v>1.88</v>
+        <v>3.54</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.1</v>
+        <v>4.25</v>
       </c>
       <c r="M86" t="n">
-        <v>3.32</v>
+        <v>2.81</v>
       </c>
       <c r="N86" t="n">
-        <v>3.38</v>
+        <v>1.97</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.38</v>
+        <v>2.01</v>
       </c>
       <c r="M87" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="N87" t="n">
-        <v>7.6</v>
+        <v>3.46</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>4.25</v>
+        <v>2.1</v>
       </c>
       <c r="M88" t="n">
-        <v>2.81</v>
+        <v>3.32</v>
       </c>
       <c r="N88" t="n">
-        <v>1.97</v>
+        <v>3.38</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.16</v>
+        <v>1.38</v>
       </c>
       <c r="M90" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="N90" t="n">
-        <v>3.54</v>
+        <v>7.6</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3.45</v>
+        <v>4.47</v>
       </c>
       <c r="M94" t="n">
-        <v>3.3</v>
+        <v>3.96</v>
       </c>
       <c r="N94" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="M95" t="n">
-        <v>5.01</v>
+        <v>4.22</v>
       </c>
       <c r="N95" t="n">
-        <v>6.73</v>
+        <v>5.86</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="M97" t="n">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="N97" t="n">
-        <v>3.39</v>
+        <v>3.05</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="M98" t="n">
-        <v>3.61</v>
+        <v>3.2</v>
       </c>
       <c r="N98" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.44</v>
+        <v>1.31</v>
       </c>
       <c r="M99" t="n">
-        <v>3.38</v>
+        <v>5.01</v>
       </c>
       <c r="N99" t="n">
-        <v>2.47</v>
+        <v>6.73</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="M100" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="N100" t="n">
-        <v>3.88</v>
+        <v>2.47</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.42</v>
+        <v>3.45</v>
       </c>
       <c r="M101" t="n">
-        <v>4.22</v>
+        <v>3.3</v>
       </c>
       <c r="N101" t="n">
-        <v>5.86</v>
+        <v>2</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.22</v>
+        <v>2.07</v>
       </c>
       <c r="M102" t="n">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="N102" t="n">
-        <v>2.97</v>
+        <v>4.76</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="M103" t="n">
-        <v>3.42</v>
+        <v>3.52</v>
       </c>
       <c r="N103" t="n">
-        <v>3.37</v>
+        <v>4.42</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,22 +12880,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="M105" t="n">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="N105" t="n">
-        <v>4.76</v>
+        <v>3.39</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="M106" t="n">
-        <v>3.52</v>
+        <v>3.42</v>
       </c>
       <c r="N106" t="n">
-        <v>4.42</v>
+        <v>3.37</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,22 +13118,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,22 +13237,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.09</v>
+        <v>2.61</v>
       </c>
       <c r="M108" t="n">
-        <v>3.38</v>
+        <v>2.93</v>
       </c>
       <c r="N108" t="n">
-        <v>3.42</v>
+        <v>2.88</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,22 +14546,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L122" t="n">
@@ -15260,22 +15260,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15887,7 +15887,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G134" t="n">

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI134"/>
+  <dimension ref="A1:AI133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>6.58</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>6.14</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.93</v>
+        <v>6.14</v>
       </c>
       <c r="M24" t="n">
-        <v>3.36</v>
+        <v>4.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.95</v>
+        <v>4.56</v>
       </c>
       <c r="N27" t="n">
-        <v>4.83</v>
+        <v>6.58</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="M49" t="n">
-        <v>2.89</v>
+        <v>3.04</v>
       </c>
       <c r="N49" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.29</v>
+        <v>1.97</v>
       </c>
       <c r="M50" t="n">
-        <v>2.99</v>
+        <v>3.14</v>
       </c>
       <c r="N50" t="n">
-        <v>3.05</v>
+        <v>3.66</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="M51" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="N51" t="n">
-        <v>2.6</v>
+        <v>3.12</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.22</v>
+        <v>2.82</v>
       </c>
       <c r="M53" t="n">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="N53" t="n">
-        <v>3.12</v>
+        <v>2.44</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,10 +6847,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="M54" t="n">
-        <v>2.79</v>
+        <v>3.44</v>
       </c>
       <c r="N54" t="n">
         <v>2.6</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>4.73</v>
+        <v>2.72</v>
       </c>
       <c r="M56" t="n">
-        <v>3.42</v>
+        <v>2.79</v>
       </c>
       <c r="N56" t="n">
-        <v>1.68</v>
+        <v>2.6</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.77</v>
+        <v>2.29</v>
       </c>
       <c r="M57" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="N57" t="n">
-        <v>2.38</v>
+        <v>3.05</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.97</v>
+        <v>4.73</v>
       </c>
       <c r="M58" t="n">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="N58" t="n">
-        <v>3.66</v>
+        <v>1.68</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="M69" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N69" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="M70" t="n">
-        <v>3.45</v>
+        <v>3.66</v>
       </c>
       <c r="N70" t="n">
-        <v>4.1</v>
+        <v>2.87</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="M75" t="n">
         <v>3.2</v>
       </c>
       <c r="N75" t="n">
-        <v>3.17</v>
+        <v>3.5</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>4.76</v>
+        <v>2.5</v>
       </c>
       <c r="M80" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N80" t="n">
-        <v>1.63</v>
+        <v>2.55</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.5</v>
+        <v>4.76</v>
       </c>
       <c r="M81" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N81" t="n">
-        <v>2.55</v>
+        <v>1.63</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="M84" t="n">
-        <v>2.86</v>
+        <v>3.32</v>
       </c>
       <c r="N84" t="n">
-        <v>4.71</v>
+        <v>3.38</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>4.25</v>
+        <v>2.01</v>
       </c>
       <c r="M86" t="n">
-        <v>2.81</v>
+        <v>3.5</v>
       </c>
       <c r="N86" t="n">
-        <v>1.97</v>
+        <v>3.46</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.01</v>
+        <v>4.25</v>
       </c>
       <c r="M87" t="n">
-        <v>3.5</v>
+        <v>2.81</v>
       </c>
       <c r="N87" t="n">
-        <v>3.46</v>
+        <v>1.97</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.38</v>
+        <v>2.16</v>
       </c>
       <c r="M90" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="N90" t="n">
-        <v>7.6</v>
+        <v>3.54</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>4.47</v>
+        <v>2.07</v>
       </c>
       <c r="M94" t="n">
-        <v>3.96</v>
+        <v>3.11</v>
       </c>
       <c r="N94" t="n">
-        <v>1.86</v>
+        <v>4.76</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,22 +11690,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.42</v>
+        <v>2.22</v>
       </c>
       <c r="M95" t="n">
-        <v>4.22</v>
+        <v>3.2</v>
       </c>
       <c r="N95" t="n">
-        <v>5.86</v>
+        <v>2.97</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="M97" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="N97" t="n">
-        <v>3.05</v>
+        <v>3.39</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.22</v>
+        <v>1.8</v>
       </c>
       <c r="M98" t="n">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="N98" t="n">
-        <v>2.97</v>
+        <v>4.42</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.31</v>
+        <v>2.26</v>
       </c>
       <c r="M99" t="n">
-        <v>5.01</v>
+        <v>3.61</v>
       </c>
       <c r="N99" t="n">
-        <v>6.73</v>
+        <v>3.05</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.44</v>
+        <v>1.31</v>
       </c>
       <c r="M100" t="n">
-        <v>3.38</v>
+        <v>5.01</v>
       </c>
       <c r="N100" t="n">
-        <v>2.47</v>
+        <v>6.73</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,22 +12404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>3.45</v>
+        <v>2</v>
       </c>
       <c r="M101" t="n">
         <v>3.3</v>
       </c>
       <c r="N101" t="n">
-        <v>2</v>
+        <v>3.88</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.07</v>
+        <v>3.45</v>
       </c>
       <c r="M102" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="N102" t="n">
-        <v>4.76</v>
+        <v>2</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="M103" t="n">
-        <v>3.52</v>
+        <v>3.42</v>
       </c>
       <c r="N103" t="n">
-        <v>4.42</v>
+        <v>3.37</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2</v>
+        <v>4.47</v>
       </c>
       <c r="M104" t="n">
-        <v>3.3</v>
+        <v>3.96</v>
       </c>
       <c r="N104" t="n">
-        <v>3.88</v>
+        <v>1.86</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,22 +12880,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="M105" t="n">
-        <v>3.5</v>
+        <v>4.22</v>
       </c>
       <c r="N105" t="n">
-        <v>3.39</v>
+        <v>5.86</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.96</v>
+        <v>2.44</v>
       </c>
       <c r="M106" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="N106" t="n">
-        <v>3.37</v>
+        <v>2.47</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,22 +13118,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,22 +13237,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,22 +13356,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,22 +15260,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15887,7 +15887,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,22 +16212,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16317,125 +16317,6 @@
         <v>0</v>
       </c>
       <c r="AI133" s="3" t="n">
-        <v>46073.875</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="n">
-        <v>46073</v>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Velež</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Željezničar</t>
-        </is>
-      </c>
-      <c r="G134" t="n">
-        <v>0</v>
-      </c>
-      <c r="H134" t="n">
-        <v>0</v>
-      </c>
-      <c r="I134" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L134" t="n">
-        <v>0</v>
-      </c>
-      <c r="M134" t="n">
-        <v>0</v>
-      </c>
-      <c r="N134" t="n">
-        <v>0</v>
-      </c>
-      <c r="O134" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
-      <c r="R134" t="n">
-        <v>0</v>
-      </c>
-      <c r="S134" t="n">
-        <v>0</v>
-      </c>
-      <c r="T134" t="n">
-        <v>0</v>
-      </c>
-      <c r="U134" t="n">
-        <v>0</v>
-      </c>
-      <c r="V134" t="n">
-        <v>0</v>
-      </c>
-      <c r="W134" t="n">
-        <v>0</v>
-      </c>
-      <c r="X134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI134" s="3" t="n">
         <v>46073.875</v>
       </c>
     </row>

--- a/jogos_2026-02-20.xlsx
+++ b/jogos_2026-02-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI133"/>
+  <dimension ref="A1:AI134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>6.14</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>6.58</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>6.14</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="M30" t="n">
-        <v>4.04</v>
+        <v>3.95</v>
       </c>
       <c r="N30" t="n">
-        <v>4.93</v>
+        <v>4.83</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.55</v>
+        <v>1.55</v>
       </c>
       <c r="M45" t="n">
-        <v>2.95</v>
+        <v>4.4</v>
       </c>
       <c r="N45" t="n">
-        <v>2.85</v>
+        <v>4.86</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,17 +6129,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.97</v>
+        <v>2.82</v>
       </c>
       <c r="M50" t="n">
-        <v>3.14</v>
+        <v>2.89</v>
       </c>
       <c r="N50" t="n">
-        <v>3.66</v>
+        <v>2.44</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="M51" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="N51" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.82</v>
+        <v>4.73</v>
       </c>
       <c r="M53" t="n">
-        <v>2.89</v>
+        <v>3.42</v>
       </c>
       <c r="N53" t="n">
-        <v>2.44</v>
+        <v>1.68</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.3</v>
+        <v>2.77</v>
       </c>
       <c r="M54" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="N54" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,17 +6962,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.72</v>
+        <v>1.97</v>
       </c>
       <c r="M56" t="n">
-        <v>2.79</v>
+        <v>3.14</v>
       </c>
       <c r="N56" t="n">
-        <v>2.6</v>
+        <v>3.66</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="M57" t="n">
-        <v>2.99</v>
+        <v>3.44</v>
       </c>
       <c r="N57" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>4.73</v>
+        <v>2.72</v>
       </c>
       <c r="M58" t="n">
-        <v>3.42</v>
+        <v>2.79</v>
       </c>
       <c r="N58" t="n">
-        <v>1.68</v>
+        <v>2.6</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,10 +8037,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="M64" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="N64" t="n">
         <v>3.5</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="M65" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N65" t="n">
-        <v>3.77</v>
+        <v>2.6</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="M70" t="n">
-        <v>3.66</v>
+        <v>3.52</v>
       </c>
       <c r="N70" t="n">
-        <v>2.87</v>
+        <v>3.5</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="M75" t="n">
-        <v>3.2</v>
+        <v>3.66</v>
       </c>
       <c r="N75" t="n">
-        <v>3.5</v>
+        <v>2.87</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.1</v>
+        <v>1.38</v>
       </c>
       <c r="M84" t="n">
-        <v>3.32</v>
+        <v>4.1</v>
       </c>
       <c r="N84" t="n">
-        <v>3.38</v>
+        <v>7.6</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>4.25</v>
+        <v>4.01</v>
       </c>
       <c r="M87" t="n">
-        <v>2.81</v>
+        <v>3.4</v>
       </c>
       <c r="N87" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.16</v>
+        <v>1.65</v>
       </c>
       <c r="M90" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="N90" t="n">
-        <v>3.54</v>
+        <v>4.47</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.07</v>
+        <v>1.31</v>
       </c>
       <c r="M94" t="n">
-        <v>3.11</v>
+        <v>5.01</v>
       </c>
       <c r="N94" t="n">
-        <v>4.76</v>
+        <v>6.73</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,22 +11690,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.22</v>
+        <v>2.07</v>
       </c>
       <c r="M95" t="n">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="N95" t="n">
-        <v>2.97</v>
+        <v>4.76</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="M98" t="n">
-        <v>3.52</v>
+        <v>3.61</v>
       </c>
       <c r="N98" t="n">
-        <v>4.42</v>
+        <v>3.05</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+    